--- a/samples/sample1/Payments_Core.xlsx
+++ b/samples/sample1/Payments_Core.xlsx
@@ -66,9 +66,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -808,9 +809,473 @@
         <v>46204</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>PC-14</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C16" t="str">
+        <v>SWIFT Payments</v>
+      </c>
+      <c r="D16" t="str">
+        <v>SWIFT gpi tracker integration</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G16" t="str">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2">
+        <v>46204</v>
+      </c>
+      <c r="I16" s="2">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>PC-15</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C17" t="str">
+        <v>SWIFT Payments</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Correspondent bank connectivity test</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G17" t="str">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2">
+        <v>46211</v>
+      </c>
+      <c r="I17" s="2">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>PC-16</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C18" t="str">
+        <v>SWIFT Payments</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Sanctions screening hook – SWIFT</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Risk</v>
+      </c>
+      <c r="G18" t="str">
+        <v>5</v>
+      </c>
+      <c r="H18" s="2">
+        <v>46225</v>
+      </c>
+      <c r="I18" s="2">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>PC-17</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C19" t="str">
+        <v>SWIFT Payments</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Payment investigation &amp; recall process</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G19" t="str">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>46239</v>
+      </c>
+      <c r="I19" s="2">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>PC-18</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C20" t="str">
+        <v>SWIFT Payments</v>
+      </c>
+      <c r="D20" t="str">
+        <v>SWIFT live cutover &amp; hypercare</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G20" t="str">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>46260</v>
+      </c>
+      <c r="I20" s="2">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>PC-19</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C21" t="str">
+        <v>SEPA Payments</v>
+      </c>
+      <c r="D21" t="str">
+        <v>SCT Inst real-time rail integration</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G21" t="str">
+        <v>10</v>
+      </c>
+      <c r="H21" s="2">
+        <v>46225</v>
+      </c>
+      <c r="I21" s="2">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>PC-20</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C22" t="str">
+        <v>SEPA Payments</v>
+      </c>
+      <c r="D22" t="str">
+        <v>SEPA direct debit mandate management</v>
+      </c>
+      <c r="E22" t="str">
+        <v>2</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G22" t="str">
+        <v>5</v>
+      </c>
+      <c r="H22" s="2">
+        <v>46239</v>
+      </c>
+      <c r="I22" s="2">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>PC-21</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C23" t="str">
+        <v>SEPA Payments</v>
+      </c>
+      <c r="D23" t="str">
+        <v>R-transaction &amp; rejection handling</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G23" t="str">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>46253</v>
+      </c>
+      <c r="I23" s="2">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>PC-22</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C24" t="str">
+        <v>SEPA Payments</v>
+      </c>
+      <c r="D24" t="str">
+        <v>SEPA scheme compliance verification</v>
+      </c>
+      <c r="E24" t="str">
+        <v>1</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Compliance</v>
+      </c>
+      <c r="G24" t="str">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>46267</v>
+      </c>
+      <c r="I24" s="2">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>PC-23</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C25" t="str">
+        <v>SEPA Payments</v>
+      </c>
+      <c r="D25" t="str">
+        <v>SEPA live cutover &amp; hypercare</v>
+      </c>
+      <c r="E25" t="str">
+        <v>1</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G25" t="str">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>46281</v>
+      </c>
+      <c r="I25" s="2">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>PC-24</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Faster Payments</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Design – Faster Payments connector</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G26" t="str">
+        <v>100</v>
+      </c>
+      <c r="H26" s="2">
+        <v>46120</v>
+      </c>
+      <c r="I26" s="2">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>PC-25</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Faster Payments</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Confirmation of payee integration</v>
+      </c>
+      <c r="E27" t="str">
+        <v>2</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G27" t="str">
+        <v>50</v>
+      </c>
+      <c r="H27" s="2">
+        <v>46155</v>
+      </c>
+      <c r="I27" s="2">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>PC-26</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Faster Payments</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Real-time fraud check hook</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Risk</v>
+      </c>
+      <c r="G28" t="str">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2">
+        <v>46169</v>
+      </c>
+      <c r="I28" s="2">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>PC-27</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Faster Payments</v>
+      </c>
+      <c r="D29" t="str">
+        <v>UAT – Faster Payments</v>
+      </c>
+      <c r="E29" t="str">
+        <v>2</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="G29" t="str">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>46204</v>
+      </c>
+      <c r="I29" s="2">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>PC-28</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Faster Payments</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Payment limit rules &amp; 24/7 monitoring</v>
+      </c>
+      <c r="E30" t="str">
+        <v>2</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="G30" t="str">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>46218</v>
+      </c>
+      <c r="I30" s="2">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>PC-29</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Payments Core</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Faster Payments</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Faster Payments live cutover</v>
+      </c>
+      <c r="E31" t="str">
+        <v>1</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="G31" t="str">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>46239</v>
+      </c>
+      <c r="I31" s="2">
+        <v>46253</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I31"/>
   </ignoredErrors>
 </worksheet>
 </file>
